--- a/ExcelTools/Excel/CfgCatalog.xlsx
+++ b/ExcelTools/Excel/CfgCatalog.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30240" windowHeight="12620"/>
+    <workbookView windowWidth="27400" windowHeight="15540"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,9 +27,57 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>ClipCfg</t>
+  </si>
+  <si>
+    <t>SkillCfg</t>
+  </si>
+  <si>
+    <t>AnimLayerCfg</t>
+  </si>
+  <si>
+    <t>CmdCfg</t>
+  </si>
+  <si>
+    <t>CmdLevelCfg</t>
+  </si>
+  <si>
+    <t>EffectCfg</t>
+  </si>
+  <si>
+    <t>AssetCfg</t>
+  </si>
+  <si>
+    <t>CharacterCfg</t>
+  </si>
+  <si>
+    <t>MonsterCfg</t>
+  </si>
+  <si>
+    <t>MonsterColonyCfg</t>
+  </si>
+  <si>
+    <t>AIModuleCfg</t>
+  </si>
+  <si>
+    <t>AICfg</t>
+  </si>
+  <si>
+    <t>MonsterControllerCfg</t>
+  </si>
+  <si>
+    <t>BuffCfg</t>
+  </si>
+  <si>
+    <t>BuffTypeCfg</t>
+  </si>
+  <si>
+    <t>TestCfg</t>
+  </si>
+  <si>
+    <t>CardCfg</t>
   </si>
 </sst>
 </file>
@@ -995,7 +1043,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="17.6"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1003,6 +1051,86 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
